--- a/docs/Ryda Operational Tracker_v01-with-status.xlsx
+++ b/docs/Ryda Operational Tracker_v01-with-status.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="16380" windowHeight="8200" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RYDA Master Tracker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RYDA Master Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -4496,7 +4496,7 @@
       <c r="I93" s="17" t="n"/>
       <c r="J93" s="17" t="inlineStr">
         <is>
-          <t>MVP scope shipped: rental listings + booking + co-ownership marketplace + member signup + KYC + admin tools. See src/app/</t>
+          <t>MVP scope shipped: rental + booking + signup + co-ownership marketplace + admin tools. May 2026 user-feedback edits applied: 3-step+5-step consolidated, deeper-math removed, FAQ link-out, Try-before-you-buy + Rent-Featured removed from cars/markets, daysPerYear 32→30, /partners B2B landing added</t>
         </is>
       </c>
       <c r="K93" s="16" t="inlineStr">
@@ -5542,7 +5542,7 @@
       <c r="I117" s="17" t="n"/>
       <c r="J117" s="17" t="inlineStr">
         <is>
-          <t>Must disclose data collection, use, sharing, retention | Drafts at /legal/{privacy,terms,cookies,accessibility,disclaimer}. Audit flagged needs expansion</t>
+          <t>Drafts at /legal/{privacy,terms,cookies,accessibility,disclaimer}. Insurance copy refresh added May 2026 ("Full coverage on every vehicle. Every co-owner is named on the policy. Every claim runs through the LLC")</t>
         </is>
       </c>
       <c r="K117" s="16" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G146" s="18" t="n"/>
@@ -6754,7 +6754,7 @@
       <c r="I146" s="17" t="n"/>
       <c r="J146" s="17" t="inlineStr">
         <is>
-          <t>Commission-only model; zero cost to partner</t>
+          <t>Partial: /partners landing page shipped from 1-pager (May 2026 commit). Real outreach + signed agreements pending</t>
         </is>
       </c>
       <c r="K146" s="16" t="inlineStr">
@@ -8602,7 +8602,7 @@
       <c r="I191" s="12" t="n"/>
       <c r="J191" s="12" t="inlineStr">
         <is>
-          <t>Waitlist API at src/app/api/waitlist/route.ts; captures email + market + interest. Signup flow at /signup</t>
+          <t>Waitlist API at src/app/api/waitlist/route.ts; signup at /signup. /partners B2B landing page added (May 2026)</t>
         </is>
       </c>
       <c r="K191" s="3" t="inlineStr">
@@ -10515,10 +10515,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="35" t="n">
         <v>0</v>
@@ -10635,10 +10635,10 @@
         <v>212</v>
       </c>
       <c r="C17" s="49" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D17" s="49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" s="49" t="n">
         <v>17</v>
